--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>Date</t>
   </si>
@@ -24,39 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>2026-06-16</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
-  </si>
-  <si>
-    <t>2026-06-22</t>
-  </si>
-  <si>
     <t>2026-06-23</t>
   </si>
   <si>
@@ -289,6 +256,15 @@
   </si>
   <si>
     <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
   </si>
   <si>
     <t>Issue</t>
@@ -347,7 +323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -369,7 +345,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>49.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="3">
@@ -380,7 +356,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="4">
@@ -391,7 +367,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="5">
@@ -402,7 +378,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="6">
@@ -413,7 +389,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>52.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="7">
@@ -424,7 +400,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>54.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="8">
@@ -435,7 +411,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>54.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="9">
@@ -446,7 +422,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>56.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="10">
@@ -457,7 +433,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="11">
@@ -468,7 +444,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="12">
@@ -479,7 +455,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>60.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="13">
@@ -490,7 +466,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="14">
@@ -501,7 +477,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="15">
@@ -512,7 +488,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="16">
@@ -523,7 +499,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="17">
@@ -534,7 +510,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="18">
@@ -545,7 +521,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="19">
@@ -556,7 +532,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="20">
@@ -567,7 +543,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="21">
@@ -578,7 +554,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="22">
@@ -589,7 +565,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="23">
@@ -600,7 +576,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="24">
@@ -611,7 +587,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="25">
@@ -622,7 +598,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="26">
@@ -633,7 +609,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>65.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="27">
@@ -644,7 +620,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>66.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="28">
@@ -655,7 +631,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>66.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="29">
@@ -666,7 +642,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="30">
@@ -677,7 +653,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="31">
@@ -688,7 +664,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="32">
@@ -699,7 +675,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="33">
@@ -710,7 +686,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="34">
@@ -721,7 +697,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="35">
@@ -732,7 +708,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="36">
@@ -743,7 +719,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>68.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="37">
@@ -754,7 +730,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>69.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="38">
@@ -765,7 +741,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>70.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="39">
@@ -776,7 +752,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>70.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="40">
@@ -787,7 +763,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="41">
@@ -798,7 +774,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="42">
@@ -809,7 +785,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="43">
@@ -820,7 +796,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>71.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="44">
@@ -831,7 +807,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>71.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="45">
@@ -842,7 +818,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>71.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="46">
@@ -853,7 +829,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>69.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="47">
@@ -864,7 +840,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="48">
@@ -875,7 +851,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="49">
@@ -886,7 +862,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="50">
@@ -897,7 +873,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="51">
@@ -908,7 +884,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="52">
@@ -919,7 +895,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="53">
@@ -930,7 +906,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="54">
@@ -963,7 +939,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="57">
@@ -974,7 +950,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="58">
@@ -985,7 +961,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="59">
@@ -996,7 +972,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="60">
@@ -1007,7 +983,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="61">
@@ -1018,7 +994,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="62">
@@ -1029,7 +1005,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="63">
@@ -1040,7 +1016,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="64">
@@ -1051,7 +1027,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="65">
@@ -1062,7 +1038,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="66">
@@ -1073,7 +1049,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="67">
@@ -1084,7 +1060,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="68">
@@ -1095,7 +1071,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="69">
@@ -1106,7 +1082,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="70">
@@ -1117,7 +1093,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="71">
@@ -1128,7 +1104,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="72">
@@ -1150,7 +1126,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="74">
@@ -1161,7 +1137,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="75">
@@ -1172,7 +1148,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="76">
@@ -1183,7 +1159,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="77">
@@ -1205,7 +1181,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="79">
@@ -1216,7 +1192,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="80">
@@ -1227,7 +1203,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="81">
@@ -1238,7 +1214,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="82">
@@ -1249,94 +1225,6 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>53.0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="B83" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C83" t="n" s="0">
-        <v>53.0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="B84" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C84" t="n" s="0">
-        <v>53.0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B85" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C85" t="n" s="0">
-        <v>53.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="B86" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C86" t="n" s="0">
-        <v>53.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>88</v>
-      </c>
-      <c r="B87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>53.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>52.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>53.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
         <v>54.0</v>
       </c>
     </row>
@@ -1352,13 +1240,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>Date</t>
   </si>
@@ -24,24 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-06-23</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>2026-06-27</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
     <t>2026-06-29</t>
   </si>
   <si>
@@ -265,6 +247,27 @@
   </si>
   <si>
     <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
   </si>
   <si>
     <t>Issue</t>
@@ -323,7 +326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -345,7 +348,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="3">
@@ -356,7 +359,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="4">
@@ -367,7 +370,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="5">
@@ -378,7 +381,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="6">
@@ -389,7 +392,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="7">
@@ -400,7 +403,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>65.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="8">
@@ -422,7 +425,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>66.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="10">
@@ -433,7 +436,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="11">
@@ -444,7 +447,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="12">
@@ -455,7 +458,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="13">
@@ -466,7 +469,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="14">
@@ -477,7 +480,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="15">
@@ -488,7 +491,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="16">
@@ -499,7 +502,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="17">
@@ -510,7 +513,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="18">
@@ -521,7 +524,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="19">
@@ -532,7 +535,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="20">
@@ -543,7 +546,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="21">
@@ -554,7 +557,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="22">
@@ -565,7 +568,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="23">
@@ -576,7 +579,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="24">
@@ -587,7 +590,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="25">
@@ -598,7 +601,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="26">
@@ -609,7 +612,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="27">
@@ -620,7 +623,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="28">
@@ -631,7 +634,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="29">
@@ -642,7 +645,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>72.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="30">
@@ -653,7 +656,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="31">
@@ -664,7 +667,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="32">
@@ -675,7 +678,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="33">
@@ -686,7 +689,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="34">
@@ -697,7 +700,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="35">
@@ -708,7 +711,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>69.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="36">
@@ -719,7 +722,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>67.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="37">
@@ -730,7 +733,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="38">
@@ -741,7 +744,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="39">
@@ -752,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="40">
@@ -763,7 +766,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="41">
@@ -774,7 +777,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="42">
@@ -785,7 +788,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="43">
@@ -873,7 +876,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="51">
@@ -884,7 +887,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="52">
@@ -895,7 +898,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="53">
@@ -906,7 +909,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="54">
@@ -917,7 +920,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="55">
@@ -928,7 +931,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="56">
@@ -939,7 +942,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="57">
@@ -950,7 +953,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="58">
@@ -961,7 +964,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="59">
@@ -972,7 +975,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="60">
@@ -983,7 +986,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="61">
@@ -994,7 +997,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="62">
@@ -1016,7 +1019,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="64">
@@ -1027,7 +1030,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="65">
@@ -1038,7 +1041,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="66">
@@ -1049,7 +1052,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="67">
@@ -1060,7 +1063,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="68">
@@ -1071,7 +1074,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="69">
@@ -1104,7 +1107,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="72">
@@ -1126,7 +1129,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="74">
@@ -1137,7 +1140,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="75">
@@ -1148,7 +1151,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="76">
@@ -1159,7 +1162,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="77">
@@ -1170,7 +1173,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="78">
@@ -1181,7 +1184,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="79">
@@ -1214,7 +1217,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="82">
@@ -1225,7 +1228,18 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B83" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C83" t="n" s="0">
+        <v>53.0</v>
       </c>
     </row>
   </sheetData>
@@ -1240,13 +1254,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>Date</t>
   </si>
@@ -24,33 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-07-01</t>
-  </si>
-  <si>
-    <t>2026-07-02</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>2026-07-05</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-07</t>
-  </si>
-  <si>
     <t>2026-07-08</t>
   </si>
   <si>
@@ -268,6 +241,36 @@
   </si>
   <si>
     <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
   </si>
   <si>
     <t>Issue</t>
@@ -326,7 +329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -348,7 +351,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="3">
@@ -359,7 +362,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="4">
@@ -370,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="5">
@@ -381,7 +384,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="6">
@@ -392,7 +395,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="7">
@@ -403,7 +406,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="8">
@@ -414,7 +417,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="9">
@@ -425,7 +428,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="10">
@@ -436,7 +439,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="11">
@@ -447,7 +450,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>66.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="12">
@@ -458,7 +461,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="13">
@@ -469,7 +472,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="14">
@@ -480,7 +483,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>67.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="15">
@@ -491,7 +494,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="16">
@@ -502,7 +505,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="17">
@@ -513,7 +516,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="18">
@@ -524,7 +527,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="19">
@@ -535,7 +538,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="20">
@@ -557,7 +560,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="22">
@@ -568,7 +571,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="23">
@@ -579,7 +582,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>72.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="24">
@@ -590,7 +593,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="25">
@@ -601,7 +604,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="26">
@@ -612,7 +615,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="27">
@@ -623,7 +626,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="28">
@@ -634,7 +637,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>71.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="29">
@@ -645,7 +648,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>69.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="30">
@@ -656,7 +659,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="31">
@@ -667,7 +670,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="32">
@@ -678,7 +681,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="33">
@@ -689,7 +692,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="34">
@@ -700,7 +703,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="35">
@@ -711,7 +714,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="36">
@@ -722,7 +725,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="37">
@@ -777,7 +780,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="42">
@@ -788,7 +791,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="43">
@@ -799,7 +802,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="44">
@@ -810,7 +813,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="45">
@@ -821,7 +824,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="46">
@@ -832,7 +835,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="47">
@@ -843,7 +846,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="48">
@@ -854,7 +857,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="49">
@@ -865,7 +868,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="50">
@@ -876,7 +879,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="51">
@@ -887,7 +890,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="52">
@@ -898,7 +901,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="53">
@@ -909,7 +912,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="54">
@@ -920,7 +923,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="55">
@@ -942,7 +945,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="57">
@@ -953,7 +956,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="58">
@@ -964,7 +967,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="59">
@@ -975,7 +978,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="60">
@@ -986,7 +989,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="61">
@@ -997,7 +1000,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="62">
@@ -1030,7 +1033,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="65">
@@ -1041,7 +1044,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="66">
@@ -1052,7 +1055,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="67">
@@ -1063,7 +1066,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="68">
@@ -1074,7 +1077,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="69">
@@ -1085,7 +1088,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="70">
@@ -1096,7 +1099,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="71">
@@ -1107,7 +1110,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="72">
@@ -1129,7 +1132,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="74">
@@ -1140,7 +1143,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="75">
@@ -1151,7 +1154,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="76">
@@ -1162,7 +1165,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="77">
@@ -1173,7 +1176,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="78">
@@ -1184,7 +1187,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="79">
@@ -1195,7 +1198,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="80">
@@ -1206,7 +1209,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="81">
@@ -1217,7 +1220,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="82">
@@ -1228,7 +1231,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="83">
@@ -1239,7 +1242,18 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B84" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C84" t="n" s="0">
+        <v>54.0</v>
       </c>
     </row>
   </sheetData>
@@ -1254,13 +1268,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>Date</t>
   </si>
@@ -24,30 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>2026-07-12</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
     <t>2026-07-16</t>
   </si>
   <si>
@@ -271,6 +247,45 @@
   </si>
   <si>
     <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
+  </si>
+  <si>
+    <t>2026-10-04</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
+  </si>
+  <si>
+    <t>2026-10-11</t>
   </si>
   <si>
     <t>Issue</t>
@@ -329,7 +344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -351,7 +366,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="3">
@@ -362,7 +377,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="4">
@@ -373,7 +388,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="5">
@@ -384,7 +399,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="6">
@@ -395,7 +410,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>68.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="7">
@@ -406,7 +421,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="8">
@@ -417,7 +432,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="9">
@@ -428,7 +443,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="10">
@@ -439,7 +454,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="11">
@@ -450,7 +465,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="12">
@@ -461,7 +476,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>70.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="13">
@@ -472,7 +487,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>70.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="14">
@@ -483,7 +498,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>72.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="15">
@@ -494,7 +509,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="16">
@@ -505,7 +520,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="17">
@@ -516,7 +531,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="18">
@@ -527,7 +542,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>71.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="19">
@@ -538,7 +553,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>71.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="20">
@@ -549,7 +564,7 @@
         <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>69.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="21">
@@ -560,7 +575,7 @@
         <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="22">
@@ -571,7 +586,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="23">
@@ -582,7 +597,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="24">
@@ -593,7 +608,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="25">
@@ -604,7 +619,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="26">
@@ -615,7 +630,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="27">
@@ -626,7 +641,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="28">
@@ -692,7 +707,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="34">
@@ -703,7 +718,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="35">
@@ -714,7 +729,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="36">
@@ -725,7 +740,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="37">
@@ -736,7 +751,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="38">
@@ -747,7 +762,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="39">
@@ -758,7 +773,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="40">
@@ -769,7 +784,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>57.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="41">
@@ -780,7 +795,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="42">
@@ -791,7 +806,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="43">
@@ -802,7 +817,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="44">
@@ -813,7 +828,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="45">
@@ -824,7 +839,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="46">
@@ -846,7 +861,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="48">
@@ -857,7 +872,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="49">
@@ -868,7 +883,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="50">
@@ -879,7 +894,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="51">
@@ -890,7 +905,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="52">
@@ -901,7 +916,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="53">
@@ -912,7 +927,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="54">
@@ -923,7 +938,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="55">
@@ -945,7 +960,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="57">
@@ -956,7 +971,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="58">
@@ -967,7 +982,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="59">
@@ -978,7 +993,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="60">
@@ -989,7 +1004,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="61">
@@ -1000,7 +1015,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="62">
@@ -1011,7 +1026,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="63">
@@ -1022,7 +1037,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="64">
@@ -1033,7 +1048,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="65">
@@ -1044,7 +1059,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="66">
@@ -1055,7 +1070,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="67">
@@ -1066,7 +1081,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="68">
@@ -1077,7 +1092,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="69">
@@ -1088,7 +1103,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="70">
@@ -1099,7 +1114,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="71">
@@ -1110,7 +1125,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="72">
@@ -1132,7 +1147,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="74">
@@ -1143,7 +1158,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="75">
@@ -1154,7 +1169,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="76">
@@ -1165,7 +1180,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="77">
@@ -1176,7 +1191,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="78">
@@ -1209,7 +1224,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="81">
@@ -1220,7 +1235,7 @@
         <v>0.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="82">
@@ -1253,7 +1268,62 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B85" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C85" t="n" s="0">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B86" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C86" t="n" s="0">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>55.0</v>
       </c>
     </row>
   </sheetData>
@@ -1268,13 +1338,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -24,24 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>2026-07-17</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>2026-07-19</t>
-  </si>
-  <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
     <t>2026-07-22</t>
   </si>
   <si>
@@ -286,6 +268,33 @@
   </si>
   <si>
     <t>2026-10-11</t>
+  </si>
+  <si>
+    <t>2026-10-12</t>
+  </si>
+  <si>
+    <t>2026-10-13</t>
+  </si>
+  <si>
+    <t>2026-10-14</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>2026-10-17</t>
+  </si>
+  <si>
+    <t>2026-10-18</t>
+  </si>
+  <si>
+    <t>2026-10-19</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
   </si>
   <si>
     <t>Issue</t>
@@ -344,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -366,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="3">
@@ -377,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="4">
@@ -388,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="5">
@@ -399,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="6">
@@ -410,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>72.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="7">
@@ -421,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="8">
@@ -432,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="9">
@@ -443,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="10">
@@ -454,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="11">
@@ -465,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>71.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="12">
@@ -476,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>69.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="13">
@@ -487,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>67.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="14">
@@ -498,7 +507,7 @@
         <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>67.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="15">
@@ -509,7 +518,7 @@
         <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="16">
@@ -520,7 +529,7 @@
         <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="17">
@@ -531,7 +540,7 @@
         <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="18">
@@ -542,7 +551,7 @@
         <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="19">
@@ -553,7 +562,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="20">
@@ -641,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="28">
@@ -652,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="29">
@@ -663,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="30">
@@ -674,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="31">
@@ -685,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="32">
@@ -696,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="33">
@@ -707,7 +716,7 @@
         <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>55.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="34">
@@ -718,7 +727,7 @@
         <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="35">
@@ -729,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="36">
@@ -740,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="37">
@@ -751,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="38">
@@ -762,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="39">
@@ -784,7 +793,7 @@
         <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="41">
@@ -795,7 +804,7 @@
         <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="42">
@@ -806,7 +815,7 @@
         <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="43">
@@ -817,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="44">
@@ -828,7 +837,7 @@
         <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="45">
@@ -839,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="46">
@@ -872,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="49">
@@ -894,7 +903,7 @@
         <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="51">
@@ -905,7 +914,7 @@
         <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="52">
@@ -916,7 +925,7 @@
         <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="53">
@@ -927,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="54">
@@ -938,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="55">
@@ -949,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="56">
@@ -982,7 +991,7 @@
         <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="59">
@@ -993,7 +1002,7 @@
         <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="60">
@@ -1004,7 +1013,7 @@
         <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="61">
@@ -1015,7 +1024,7 @@
         <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="62">
@@ -1026,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="63">
@@ -1037,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="64">
@@ -1081,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="68">
@@ -1092,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="69">
@@ -1103,7 +1112,7 @@
         <v>0.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="70">
@@ -1114,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="71">
@@ -1125,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="72">
@@ -1147,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="74">
@@ -1169,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="76">
@@ -1213,7 +1222,7 @@
         <v>0.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="80">
@@ -1224,7 +1233,7 @@
         <v>0.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="81">
@@ -1246,7 +1255,7 @@
         <v>0.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="83">
@@ -1257,7 +1266,7 @@
         <v>0.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="84">
@@ -1268,7 +1277,7 @@
         <v>0.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="85">
@@ -1324,6 +1333,39 @@
       </c>
       <c r="C89" t="n" s="0">
         <v>55.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B91" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C91" t="n" s="0">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B92" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C92" t="n" s="0">
+        <v>56.0</v>
       </c>
     </row>
   </sheetData>
@@ -1338,13 +1380,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,12 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-07-22</t>
-  </si>
-  <si>
-    <t>2026-07-23</t>
-  </si>
-  <si>
     <t>2026-07-24</t>
   </si>
   <si>
@@ -295,6 +289,12 @@
   </si>
   <si>
     <t>2026-10-20</t>
+  </si>
+  <si>
+    <t>2026-10-21</t>
+  </si>
+  <si>
+    <t>2026-10-22</t>
   </si>
   <si>
     <t>Issue</t>
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>71.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>69.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>67.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>67.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="9">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>66.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>66.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="12">
@@ -485,7 +485,7 @@
         <v>0.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +496,7 @@
         <v>0.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="14">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="27">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>55.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="28">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="31">
@@ -694,7 +694,7 @@
         <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +705,7 @@
         <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="33">
@@ -771,7 +771,7 @@
         <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="39">
@@ -782,7 +782,7 @@
         <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="40">
@@ -859,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="47">
@@ -881,7 +881,7 @@
         <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="49">
@@ -892,7 +892,7 @@
         <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="50">
@@ -969,7 +969,7 @@
         <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="57">
@@ -980,7 +980,7 @@
         <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="58">
@@ -1068,7 +1068,7 @@
         <v>0.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="66">
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="67">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1145,7 @@
         <v>0.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="73">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="74">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>55.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="77">
@@ -1200,7 +1200,7 @@
         <v>0.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="78">
@@ -1211,7 +1211,7 @@
         <v>0.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="79">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>55.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="92">
@@ -1365,7 +1365,7 @@
         <v>0.0</v>
       </c>
       <c r="C92" t="n" s="0">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/HTTPS.xlsx
+++ b/gsc-export/HTTPS.xlsx
@@ -24,15 +24,6 @@
     <t>HTTPS URLs</t>
   </si>
   <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>2026-07-26</t>
-  </si>
-  <si>
     <t>2026-07-27</t>
   </si>
   <si>
@@ -295,6 +286,15 @@
   </si>
   <si>
     <t>2026-10-22</t>
+  </si>
+  <si>
+    <t>2026-10-23</t>
+  </si>
+  <si>
+    <t>2026-10-24</t>
+  </si>
+  <si>
+    <t>2026-10-25</t>
   </si>
   <si>
     <t>Issue</t>
@@ -375,7 +375,7 @@
         <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="3">
@@ -386,7 +386,7 @@
         <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>71.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>69.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="5">
@@ -408,7 +408,7 @@
         <v>0.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>67.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="6">
@@ -419,7 +419,7 @@
         <v>0.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>67.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>66.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="8">
@@ -441,7 +441,7 @@
         <v>0.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>66.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="9">
@@ -452,7 +452,7 @@
         <v>0.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>66.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="10">
@@ -463,7 +463,7 @@
         <v>0.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>63.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="11">
@@ -474,7 +474,7 @@
         <v>0.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="23">
@@ -606,7 +606,7 @@
         <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="24">
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>57.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>55.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="26">
@@ -650,7 +650,7 @@
         <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="29">
@@ -672,7 +672,7 @@
         <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>54.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="30">
@@ -683,7 +683,7 @@
         <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="31">
@@ -738,7 +738,7 @@
         <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="36">
@@ -749,7 +749,7 @@
         <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="37">
@@ -760,7 +760,7 @@
         <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="38">
@@ -826,7 +826,7 @@
         <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="44">
@@ -848,7 +848,7 @@
         <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="46">
@@ -859,7 +859,7 @@
         <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +870,7 @@
         <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="48">
@@ -936,7 +936,7 @@
         <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="54">
@@ -947,7 +947,7 @@
         <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="55">
@@ -958,7 +958,7 @@
         <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="56">
@@ -1035,7 +1035,7 @@
         <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="63">
@@ -1046,7 +1046,7 @@
         <v>0.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="64">
@@ -1057,7 +1057,7 @@
         <v>0.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="65">
@@ -1090,7 +1090,7 @@
         <v>0.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         <v>0.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>54.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="69">
@@ -1123,7 +1123,7 @@
         <v>0.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="71">
@@ -1134,7 +1134,7 @@
         <v>0.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="72">
@@ -1156,7 +1156,7 @@
         <v>0.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>55.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         <v>0.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1178,7 @@
         <v>0.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="76">
@@ -1189,7 +1189,7 @@
         <v>0.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="77">
@@ -1310,7 +1310,7 @@
         <v>0.0</v>
       </c>
       <c r="C87" t="n" s="0">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="88">
@@ -1321,7 +1321,7 @@
         <v>0.0</v>
       </c>
       <c r="C88" t="n" s="0">
-        <v>55.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="89">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="C89" t="n" s="0">
-        <v>55.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="90">
@@ -1343,7 +1343,7 @@
         <v>0.0</v>
       </c>
       <c r="C90" t="n" s="0">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="91">
@@ -1354,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="C91" t="n" s="0">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="92">
@@ -1365,7 +1365,7 @@
         <v>0.0</v>
       </c>
       <c r="C92" t="n" s="0">
-        <v>57.0</v>
+        <v>53.0</v>
       </c>
     </row>
   </sheetData>
